--- a/cet4/result/75_校园音乐_少女追梦的逆袭路/75_校园音乐_少女追梦的逆袭路_学习版.xlsx
+++ b/cet4/result/75_校园音乐_少女追梦的逆袭路/75_校园音乐_少女追梦的逆袭路_学习版.xlsx
@@ -397,773 +397,703 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D49"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>tropical</v>
       </c>
       <c r="B2" t="str">
-        <v>tropical</v>
+        <v>/ˈtrɑːpɪkl/</v>
       </c>
       <c r="C2" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>热带的</v>
       </c>
-      <c r="D2" t="str">
-        <v>tropical(热带的)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>campus</v>
       </c>
       <c r="B3" t="str">
-        <v>campus</v>
+        <v>/ˈkæmpəs/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>校园</v>
       </c>
-      <c r="D3" t="str">
-        <v>campus(校园)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>enthusiasm</v>
       </c>
       <c r="B4" t="str">
-        <v>enthusiasm</v>
+        <v>/ɪnˈθuːziæzəm/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>热情</v>
       </c>
-      <c r="D4" t="str">
-        <v>enthusiasm(热情)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>eastern</v>
       </c>
       <c r="B5" t="str">
-        <v>eastern</v>
+        <v>/ˈiːstərn/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>东方的</v>
       </c>
-      <c r="D5" t="str">
-        <v>eastern(东方的)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>famous</v>
       </c>
       <c r="B6" t="str">
-        <v>famous</v>
+        <v>/ˈfeɪməs/</v>
       </c>
       <c r="C6" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>著名的</v>
       </c>
-      <c r="D6" t="str">
-        <v>famous(著名的)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>magnet</v>
       </c>
       <c r="B7" t="str">
-        <v>magnet</v>
+        <v>/ˈmæɡnət/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>磁铁</v>
       </c>
-      <c r="D7" t="str">
-        <v>magnet(磁铁)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>unusual</v>
       </c>
       <c r="B8" t="str">
-        <v>unusual</v>
+        <v>/ʌnˈjuːʒuəl/</v>
       </c>
       <c r="C8" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>不寻常的</v>
       </c>
-      <c r="D8" t="str">
-        <v>unusual(不寻常的)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>bitter</v>
       </c>
       <c r="B9" t="str">
-        <v>bitter</v>
+        <v>/ˈbɪtər/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./vt./v./adj./adv.</v>
+      </c>
+      <c r="D9" t="str">
         <v>苦的</v>
       </c>
-      <c r="D9" t="str">
-        <v>bitter(苦的)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>Chinese</v>
       </c>
       <c r="B10" t="str">
-        <v>Chinese</v>
+        <v>/ˌtʃaɪˈniːz/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>中文</v>
       </c>
-      <c r="D10" t="str">
-        <v>Chinese(中文)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>grant</v>
       </c>
       <c r="B11" t="str">
-        <v>grant</v>
+        <v>/ɡrænt/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D11" t="str">
         <v>拨款</v>
       </c>
-      <c r="D11" t="str">
-        <v>grant(拨款)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>anybody</v>
       </c>
       <c r="B12" t="str">
-        <v>anybody</v>
+        <v>/ˈenibɑːdi,ˈenibʌdi/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D12" t="str">
         <v>任何人</v>
       </c>
-      <c r="D12" t="str">
-        <v>anybody(任何人)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>mosquito</v>
       </c>
       <c r="B13" t="str">
-        <v>mosquito</v>
+        <v>/məˈskiːtoʊ/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>蚊子</v>
       </c>
-      <c r="D13" t="str">
-        <v>mosquito(蚊子)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>blanket</v>
       </c>
       <c r="B14" t="str">
-        <v>blanket</v>
+        <v>/ˈblæŋkɪt/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>毛毯</v>
       </c>
-      <c r="D14" t="str">
-        <v>blanket(毛毯)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>critic</v>
       </c>
       <c r="B15" t="str">
-        <v>critic</v>
+        <v>/ˈkrɪtɪk/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>批评家</v>
       </c>
-      <c r="D15" t="str">
-        <v>critic(批评家)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>mathematical</v>
       </c>
       <c r="B16" t="str">
-        <v>mathematical</v>
+        <v>/ˌmæθəˈmætɪkl/</v>
       </c>
       <c r="C16" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D16" t="str">
         <v>数学的</v>
       </c>
-      <c r="D16" t="str">
-        <v>mathematical(数学的)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>sensitive</v>
       </c>
       <c r="B17" t="str">
-        <v>sensitive</v>
+        <v>/ˈsensətɪv/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>敏感的</v>
       </c>
-      <c r="D17" t="str">
-        <v>sensitive(敏感的)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>simplicity</v>
       </c>
       <c r="B18" t="str">
-        <v>anybody</v>
+        <v>/sɪmˈplɪsəti/</v>
       </c>
       <c r="C18" t="str">
-        <v>任何人</v>
+        <v>n.</v>
       </c>
       <c r="D18" t="str">
-        <v>anybody(任何人)📢</v>
+        <v>朴素</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>concert</v>
       </c>
       <c r="B19" t="str">
-        <v>simplicity</v>
+        <v>/ˈkɑːnsərt/</v>
       </c>
       <c r="C19" t="str">
-        <v>朴素</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D19" t="str">
-        <v>simplicity(朴素)📢</v>
+        <v>音乐会</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>needless</v>
       </c>
       <c r="B20" t="str">
-        <v>concert</v>
+        <v>/ˈniːdləs/</v>
       </c>
       <c r="C20" t="str">
-        <v>音乐会</v>
+        <v>adj.</v>
       </c>
       <c r="D20" t="str">
-        <v>concert(音乐会)📢</v>
+        <v>不必要的</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>coil</v>
       </c>
       <c r="B21" t="str">
-        <v>needless</v>
+        <v>/kɔɪl/</v>
       </c>
       <c r="C21" t="str">
-        <v>不必要的</v>
+        <v>v.</v>
       </c>
       <c r="D21" t="str">
-        <v>needless(不必要的)📢</v>
+        <v>盘绕</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>rumour</v>
       </c>
       <c r="B22" t="str">
-        <v>coil</v>
+        <v>/ˈruːmər/</v>
       </c>
       <c r="C22" t="str">
-        <v>盘绕</v>
+        <v>n./vt.</v>
       </c>
       <c r="D22" t="str">
-        <v>coil(盘绕)📢</v>
+        <v>谣言</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>rebel</v>
       </c>
       <c r="B23" t="str">
-        <v>rumour</v>
+        <v>/ˈrebl/</v>
       </c>
       <c r="C23" t="str">
-        <v>谣言</v>
+        <v>n./v./adj.</v>
       </c>
       <c r="D23" t="str">
-        <v>rumour(谣言)📢</v>
+        <v>造反者</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>independence</v>
       </c>
       <c r="B24" t="str">
-        <v>rebel</v>
+        <v>/ˌɪndɪˈpendəns/</v>
       </c>
       <c r="C24" t="str">
-        <v>造反者</v>
+        <v>n.</v>
       </c>
       <c r="D24" t="str">
-        <v>rebel(造反者)📢</v>
+        <v>独立性</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>push</v>
       </c>
       <c r="B25" t="str">
-        <v>independence</v>
+        <v>/pʊʃ/</v>
       </c>
       <c r="C25" t="str">
-        <v>独立性</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D25" t="str">
-        <v>independence(独立性)📢</v>
+        <v>推动</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>delay</v>
       </c>
       <c r="B26" t="str">
-        <v>push</v>
+        <v>/dɪˈleɪ/</v>
       </c>
       <c r="C26" t="str">
-        <v>推动</v>
+        <v>n./v.</v>
       </c>
       <c r="D26" t="str">
-        <v>push(推动)📢</v>
+        <v>延迟</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>reliance</v>
       </c>
       <c r="B27" t="str">
-        <v>delay</v>
+        <v>/rɪˈlaɪəns/</v>
       </c>
       <c r="C27" t="str">
-        <v>延迟</v>
+        <v>n.</v>
       </c>
       <c r="D27" t="str">
-        <v>delay(延迟)📢</v>
+        <v>信赖</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>coin</v>
       </c>
       <c r="B28" t="str">
-        <v>reliance</v>
+        <v>/kɔɪn/</v>
       </c>
       <c r="C28" t="str">
-        <v>信赖</v>
+        <v>n./vt.</v>
       </c>
       <c r="D28" t="str">
-        <v>reliance(信赖)📢</v>
+        <v>硬币</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>surprisingly</v>
       </c>
       <c r="B29" t="str">
-        <v>coin</v>
+        <v>/sərˈpraɪzɪŋli/</v>
       </c>
       <c r="C29" t="str">
-        <v>硬币</v>
+        <v>v./adv.</v>
       </c>
       <c r="D29" t="str">
-        <v>coin(硬币)📢</v>
+        <v>惊人地</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>wait</v>
       </c>
       <c r="B30" t="str">
-        <v>surprisingly</v>
+        <v>/weɪt/</v>
       </c>
       <c r="C30" t="str">
-        <v>惊人地</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D30" t="str">
-        <v>surprisingly(惊人地)📢</v>
+        <v>等待</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>develop</v>
       </c>
       <c r="B31" t="str">
-        <v>famous</v>
+        <v>/dɪˈveləp/</v>
       </c>
       <c r="C31" t="str">
-        <v>著名的</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D31" t="str">
-        <v>famous(著名的)📢</v>
+        <v>开发</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>swell</v>
       </c>
       <c r="B32" t="str">
-        <v>wait</v>
+        <v>/swel/</v>
       </c>
       <c r="C32" t="str">
-        <v>等待</v>
+        <v>v.</v>
       </c>
       <c r="D32" t="str">
-        <v>wait(等待)📢</v>
+        <v>膨胀</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>smart</v>
       </c>
       <c r="B33" t="str">
-        <v>develop</v>
+        <v>/smɑːrt/</v>
       </c>
       <c r="C33" t="str">
-        <v>开发</v>
+        <v>n./adj.</v>
       </c>
       <c r="D33" t="str">
-        <v>develop(开发)📢</v>
+        <v>聪明的</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>rocket</v>
       </c>
       <c r="B34" t="str">
-        <v>swell</v>
+        <v>/ˈrɑːkɪt/</v>
       </c>
       <c r="C34" t="str">
-        <v>膨胀</v>
+        <v>n./v.</v>
       </c>
       <c r="D34" t="str">
-        <v>swell(膨胀)📢</v>
+        <v>火箭</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>gun</v>
       </c>
       <c r="B35" t="str">
-        <v>smart</v>
+        <v>/ɡʌn/</v>
       </c>
       <c r="C35" t="str">
-        <v>聪明的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D35" t="str">
-        <v>smart(聪明的)📢</v>
+        <v>枪</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>shoot</v>
       </c>
       <c r="B36" t="str">
-        <v>rocket</v>
+        <v>/ʃuːt/</v>
       </c>
       <c r="C36" t="str">
-        <v>火箭</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D36" t="str">
-        <v>rocket(火箭)📢</v>
+        <v>拍摄</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>transformation</v>
       </c>
       <c r="B37" t="str">
-        <v>gun</v>
+        <v>/ˌtrænsfərˈmeɪʃn/</v>
       </c>
       <c r="C37" t="str">
-        <v>枪</v>
+        <v>n.</v>
       </c>
       <c r="D37" t="str">
-        <v>gun(枪)📢</v>
+        <v>转化</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>boast</v>
       </c>
       <c r="B38" t="str">
-        <v>shoot</v>
+        <v>/boʊst/</v>
       </c>
       <c r="C38" t="str">
-        <v>拍摄</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D38" t="str">
-        <v>shoot(拍摄)📢</v>
+        <v>夸口</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>promote</v>
       </c>
       <c r="B39" t="str">
-        <v>transformation</v>
+        <v>/prəˈmoʊt/</v>
       </c>
       <c r="C39" t="str">
-        <v>转化</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D39" t="str">
-        <v>transformation(转化)📢</v>
+        <v>提升</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>nuclear</v>
       </c>
       <c r="B40" t="str">
-        <v>surprisingly</v>
+        <v>/ˈnuːkliər/</v>
       </c>
       <c r="C40" t="str">
-        <v>惊人地</v>
+        <v>adj.</v>
       </c>
       <c r="D40" t="str">
-        <v>surprisingly(惊人地)📢</v>
+        <v>核能</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>invisible</v>
       </c>
       <c r="B41" t="str">
-        <v>boast</v>
+        <v>/ɪnˈvɪzəbl/</v>
       </c>
       <c r="C41" t="str">
-        <v>夸口</v>
+        <v>adj.</v>
       </c>
       <c r="D41" t="str">
-        <v>boast(夸口)📢</v>
+        <v>看不见的</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>possibility</v>
       </c>
       <c r="B42" t="str">
-        <v>promote</v>
+        <v>/ˌpɑːsəˈbɪləti/</v>
       </c>
       <c r="C42" t="str">
-        <v>提升</v>
+        <v>n.</v>
       </c>
       <c r="D42" t="str">
-        <v>promote(提升)📢</v>
+        <v>可能性</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>employ</v>
       </c>
       <c r="B43" t="str">
-        <v>unusual</v>
+        <v>/ɪmˈplɔɪ/</v>
       </c>
       <c r="C43" t="str">
-        <v>不寻常的</v>
+        <v>n./vt.</v>
       </c>
       <c r="D43" t="str">
-        <v>unusual(不寻常的)📢</v>
+        <v>雇用</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>nowadays</v>
       </c>
       <c r="B44" t="str">
-        <v>nuclear</v>
+        <v>/ˈnaʊədeɪz/</v>
       </c>
       <c r="C44" t="str">
-        <v>核能</v>
+        <v>n./v./adv.</v>
       </c>
       <c r="D44" t="str">
-        <v>nuclear(核能)📢</v>
+        <v>现今</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>bring</v>
       </c>
       <c r="B45" t="str">
-        <v>invisible</v>
+        <v>/brɪŋ/</v>
       </c>
       <c r="C45" t="str">
-        <v>看不见的</v>
+        <v>n./vt.</v>
       </c>
       <c r="D45" t="str">
-        <v>invisible(看不见的)📢</v>
+        <v>带来</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>anywhere</v>
       </c>
       <c r="B46" t="str">
-        <v>possibility</v>
+        <v>/ˈeniwer/</v>
       </c>
       <c r="C46" t="str">
-        <v>可能性</v>
+        <v>n./v./adv.</v>
       </c>
       <c r="D46" t="str">
-        <v>possibility(可能性)📢</v>
+        <v>任何地方</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>gaseous</v>
       </c>
       <c r="B47" t="str">
-        <v>critic</v>
+        <v>/ˈɡæsiəs,ˈɡeɪsiəs/</v>
       </c>
       <c r="C47" t="str">
-        <v>批评家</v>
+        <v>adj.</v>
       </c>
       <c r="D47" t="str">
-        <v>critic(批评家)📢</v>
+        <v>气态的</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>reasonable</v>
       </c>
       <c r="B48" t="str">
-        <v>employ</v>
+        <v>/ˈriːznəbl/</v>
       </c>
       <c r="C48" t="str">
-        <v>雇用</v>
+        <v>adj.</v>
       </c>
       <c r="D48" t="str">
-        <v>employ(雇用)📢</v>
+        <v>合理的</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>territory</v>
       </c>
       <c r="B49" t="str">
-        <v>nowadays</v>
+        <v>/ˈterətɔːri/</v>
       </c>
       <c r="C49" t="str">
-        <v>现今</v>
+        <v>n.</v>
       </c>
       <c r="D49" t="str">
-        <v>nowadays(现今)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>bring</v>
-      </c>
-      <c r="C50" t="str">
-        <v>带来</v>
-      </c>
-      <c r="D50" t="str">
-        <v>bring(带来)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>anywhere</v>
-      </c>
-      <c r="C51" t="str">
-        <v>任何地方</v>
-      </c>
-      <c r="D51" t="str">
-        <v>anywhere(任何地方)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>gaseous</v>
-      </c>
-      <c r="C52" t="str">
-        <v>气态的</v>
-      </c>
-      <c r="D52" t="str">
-        <v>gaseous(气态的)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>reasonable</v>
-      </c>
-      <c r="C53" t="str">
-        <v>合理的</v>
-      </c>
-      <c r="D53" t="str">
-        <v>reasonable(合理的)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>territory</v>
-      </c>
-      <c r="C54" t="str">
         <v>领域</v>
-      </c>
-      <c r="D54" t="str">
-        <v>territory(领域)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D49"/>
   </ignoredErrors>
 </worksheet>
 </file>